--- a/MavenBook/src/test/resources/PurchaseBillData.xlsx
+++ b/MavenBook/src/test/resources/PurchaseBillData.xlsx
@@ -4,21 +4,18 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18495" windowHeight="7005" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PurchaseBillHeader" sheetId="1" r:id="rId1"/>
     <sheet name="PurchaseBillItems" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>Customer Name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Item Name</t>
   </si>
@@ -44,32 +41,98 @@
     <t>Reference Number</t>
   </si>
   <si>
-    <t>Automated one</t>
-  </si>
-  <si>
-    <t>BP Apparatus</t>
-  </si>
-  <si>
-    <t>Test S2</t>
-  </si>
-  <si>
     <t>Net 30</t>
   </si>
   <si>
-    <t>23-12-2025</t>
-  </si>
-  <si>
-    <t>24-12-2025</t>
-  </si>
-  <si>
-    <t>30-12-2025</t>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>Discount Level</t>
+  </si>
+  <si>
+    <t>Discount After-Before Tax</t>
+  </si>
+  <si>
+    <t>Discount TType</t>
+  </si>
+  <si>
+    <t>DiscountT</t>
+  </si>
+  <si>
+    <t>Discount Account</t>
+  </si>
+  <si>
+    <t>Customer Notes</t>
+  </si>
+  <si>
+    <t>Terms And Conditions</t>
+  </si>
+  <si>
+    <t>Save As</t>
+  </si>
+  <si>
+    <t>Price List</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Purchase Discount</t>
+  </si>
+  <si>
+    <t>notex</t>
+  </si>
+  <si>
+    <t>termsx</t>
+  </si>
+  <si>
+    <t>Discount Type</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>Exclusive</t>
+  </si>
+  <si>
+    <t>At Line Item Level</t>
+  </si>
+  <si>
+    <t>15-04-2026</t>
+  </si>
+  <si>
+    <t>7426-2</t>
+  </si>
+  <si>
+    <t>SAVE AND APPROVE</t>
+  </si>
+  <si>
+    <t>After Tax</t>
+  </si>
+  <si>
+    <t>Notebook 100</t>
+  </si>
+  <si>
+    <t>Pencils 10</t>
+  </si>
+  <si>
+    <t>Desk Note</t>
+  </si>
+  <si>
+    <t>Coffe</t>
+  </si>
+  <si>
+    <t>Subin</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,6 +156,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -102,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -110,11 +184,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -141,6 +230,13 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,64 +542,206 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="19.42578125" style="7" customWidth="1"/>
     <col min="3" max="3" width="16" style="7" customWidth="1"/>
     <col min="4" max="4" width="26.140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" style="7" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" style="6" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="6"/>
+    <col min="7" max="7" width="13.42578125" style="6" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" style="6" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="18.42578125" style="6" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" style="6" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" style="6" customWidth="1"/>
+    <col min="16" max="16" width="11.85546875" style="6" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
+      <c r="G2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="7"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
       <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="15"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="7"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
       <c r="B4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="15"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="12"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="15"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="12"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="15"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="12"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="15"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="12"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E9" s="15"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E10" s="15"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E11" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -513,34 +751,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="14">
+        <v>5</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="14">
         <v>10</v>
       </c>
-      <c r="C2">
-        <v>20</v>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="14">
+        <v>5</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="14">
+        <v>5</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="14">
+        <v>5</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="14">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/MavenBook/src/test/resources/PurchaseBillData.xlsx
+++ b/MavenBook/src/test/resources/PurchaseBillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="54">
   <si>
     <t>Item Name</t>
   </si>
@@ -74,6 +74,9 @@
     <t>Price List</t>
   </si>
   <si>
+    <t>Before Tax</t>
+  </si>
+  <si>
     <t>%</t>
   </si>
   <si>
@@ -98,41 +101,89 @@
     <t>Exclusive</t>
   </si>
   <si>
+    <t>At transaction level</t>
+  </si>
+  <si>
     <t>At Line Item Level</t>
   </si>
   <si>
-    <t>15-04-2026</t>
-  </si>
-  <si>
-    <t>7426-2</t>
-  </si>
-  <si>
     <t>SAVE AND APPROVE</t>
   </si>
   <si>
     <t>After Tax</t>
   </si>
   <si>
-    <t>Notebook 100</t>
-  </si>
-  <si>
-    <t>Pencils 10</t>
-  </si>
-  <si>
-    <t>Desk Note</t>
-  </si>
-  <si>
-    <t>Coffe</t>
-  </si>
-  <si>
-    <t>Subin</t>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Inclusive</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>15-05-2026</t>
+  </si>
+  <si>
+    <t>25426-1</t>
+  </si>
+  <si>
+    <t>25426-2</t>
+  </si>
+  <si>
+    <t>25426-3</t>
+  </si>
+  <si>
+    <t>25426-4</t>
+  </si>
+  <si>
+    <t>25426-5</t>
+  </si>
+  <si>
+    <t>25426-6</t>
+  </si>
+  <si>
+    <t>Non VAT Registered</t>
+  </si>
+  <si>
+    <t>25426-7</t>
+  </si>
+  <si>
+    <t>25426-8</t>
+  </si>
+  <si>
+    <t>25426-9</t>
+  </si>
+  <si>
+    <t>25426-10</t>
+  </si>
+  <si>
+    <t>Gcc VAT Registered</t>
+  </si>
+  <si>
+    <t>Gcc Non VAT Registered</t>
+  </si>
+  <si>
+    <t>US Vendor</t>
+  </si>
+  <si>
+    <t>Notepad Medium</t>
+  </si>
+  <si>
+    <t>Oppo F15</t>
+  </si>
+  <si>
+    <t>Service 1</t>
+  </si>
+  <si>
+    <t>Pear</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +217,19 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -203,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -238,6 +302,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,10 +615,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.42578125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="7" customWidth="1"/>
     <col min="3" max="3" width="16" style="7" customWidth="1"/>
     <col min="4" max="4" width="26.140625" style="7" customWidth="1"/>
     <col min="5" max="5" width="21.140625" style="7" customWidth="1"/>
@@ -615,42 +689,42 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2">
         <v>10</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O2" s="12" t="s">
         <v>30</v>
@@ -658,90 +732,2054 @@
       <c r="P2" s="7"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="15"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="12"/>
+      <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="12" t="s">
+        <v>30</v>
+      </c>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="B4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="15"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="12"/>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4">
+        <v>10</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="15"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="12"/>
+      <c r="A5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="15"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="12"/>
+      <c r="A6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6">
+        <v>10</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="15"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="12"/>
+      <c r="A7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E8" s="15"/>
+      <c r="A8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P8" s="7"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E9" s="15"/>
+      <c r="A9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E10" s="15"/>
+      <c r="A10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E11" s="15"/>
+      <c r="A11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P11" s="7"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P13" s="7"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14">
+        <v>10</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O15" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O16" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P16" s="7"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O17" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="P17" s="7"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18">
+        <v>10</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19">
+        <v>10</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O20" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O22" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23">
+        <v>10</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O23" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24">
+        <v>10</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O24" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" t="s">
+        <v>32</v>
+      </c>
+      <c r="K25">
+        <v>10</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26">
+        <v>10</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27">
+        <v>10</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28">
+        <v>10</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" t="s">
+        <v>32</v>
+      </c>
+      <c r="K29">
+        <v>10</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O29" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K30">
+        <v>10</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31">
+        <v>10</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O31" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="19">
+        <v>10</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M32" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O32" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="19">
+        <v>10</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K34" s="19">
+        <v>10</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K35" s="19">
+        <v>10</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M35" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O35" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="19">
+        <v>10</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M36" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O36" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="19">
+        <v>10</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O37" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="19">
+        <v>10</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M38" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O38" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I39" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K39" s="19">
+        <v>10</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M39" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I40" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K40" s="19">
+        <v>10</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M40" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O40" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="19">
+        <v>10</v>
+      </c>
+      <c r="L41" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M41" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O41" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="19">
+        <v>10</v>
+      </c>
+      <c r="L42" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M42" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O42" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="19">
+        <v>10</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M43" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K44" s="19">
+        <v>10</v>
+      </c>
+      <c r="L44" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M44" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N44" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I45" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" s="19">
+        <v>10</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M45" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O45" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="19">
+        <v>10</v>
+      </c>
+      <c r="L46" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M46" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N46" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I47" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="19">
+        <v>10</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M47" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N47" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O47" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="19">
+        <v>10</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M48" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N48" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O48" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K49" s="19">
+        <v>10</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M49" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N49" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O49" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K50" s="19">
+        <v>10</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M50" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N50" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O50" s="20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="I51" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="19">
+        <v>10</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="M51" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="O51" s="20" t="s">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -751,7 +2789,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" style="1" customWidth="1"/>
@@ -772,24 +2810,24 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C2" s="14">
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="14">
         <v>10</v>
@@ -797,16 +2835,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C3" s="14">
         <v>5</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="14">
         <v>10</v>
@@ -814,16 +2852,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C4" s="14">
         <v>5</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="14">
         <v>10</v>
@@ -831,20 +2869,262 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="14">
+        <v>52</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="14">
         <v>5</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="14">
-        <v>10</v>
-      </c>
+      <c r="D6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="14">
+        <v>5</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="14">
+        <v>5</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="14">
+        <v>5</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="14">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="14">
+        <v>5</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="14">
+        <v>5</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="14">
+        <v>5</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="14">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="14">
+        <v>5</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MavenBook/src/test/resources/PurchaseBillData.xlsx
+++ b/MavenBook/src/test/resources/PurchaseBillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="94">
   <si>
     <t>Item Name</t>
   </si>
@@ -41,9 +41,6 @@
     <t>Reference Number</t>
   </si>
   <si>
-    <t>Net 30</t>
-  </si>
-  <si>
     <t>Tax</t>
   </si>
   <si>
@@ -119,64 +116,187 @@
     <t>Inclusive</t>
   </si>
   <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>15-05-2026</t>
-  </si>
-  <si>
-    <t>25426-1</t>
-  </si>
-  <si>
-    <t>25426-2</t>
-  </si>
-  <si>
-    <t>25426-3</t>
-  </si>
-  <si>
-    <t>25426-4</t>
-  </si>
-  <si>
-    <t>25426-5</t>
-  </si>
-  <si>
-    <t>25426-6</t>
-  </si>
-  <si>
-    <t>Non VAT Registered</t>
-  </si>
-  <si>
-    <t>25426-7</t>
-  </si>
-  <si>
-    <t>25426-8</t>
-  </si>
-  <si>
-    <t>25426-9</t>
-  </si>
-  <si>
-    <t>25426-10</t>
-  </si>
-  <si>
-    <t>Gcc VAT Registered</t>
-  </si>
-  <si>
-    <t>Gcc Non VAT Registered</t>
-  </si>
-  <si>
-    <t>US Vendor</t>
-  </si>
-  <si>
-    <t>Notepad Medium</t>
-  </si>
-  <si>
-    <t>Oppo F15</t>
-  </si>
-  <si>
     <t>Service 1</t>
   </si>
   <si>
-    <t>Pear</t>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>VAT Reg Vendor</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Non Vat Vendor</t>
+  </si>
+  <si>
+    <t>GCC Vat Reg Oman</t>
+  </si>
+  <si>
+    <t>GCC Non Vat Oman</t>
+  </si>
+  <si>
+    <t>None GCC V</t>
+  </si>
+  <si>
+    <t>15-08-2026</t>
+  </si>
+  <si>
+    <t>5826-1</t>
+  </si>
+  <si>
+    <t>5826-2</t>
+  </si>
+  <si>
+    <t>5826-3</t>
+  </si>
+  <si>
+    <t>5826-4</t>
+  </si>
+  <si>
+    <t>5826-5</t>
+  </si>
+  <si>
+    <t>5826-6</t>
+  </si>
+  <si>
+    <t>5826-7</t>
+  </si>
+  <si>
+    <t>5826-8</t>
+  </si>
+  <si>
+    <t>5826-9</t>
+  </si>
+  <si>
+    <t>5826-10</t>
+  </si>
+  <si>
+    <t>5826-11</t>
+  </si>
+  <si>
+    <t>5826-12</t>
+  </si>
+  <si>
+    <t>5826-13</t>
+  </si>
+  <si>
+    <t>5826-14</t>
+  </si>
+  <si>
+    <t>5826-15</t>
+  </si>
+  <si>
+    <t>5826-16</t>
+  </si>
+  <si>
+    <t>5826-17</t>
+  </si>
+  <si>
+    <t>5826-18</t>
+  </si>
+  <si>
+    <t>5826-19</t>
+  </si>
+  <si>
+    <t>5826-20</t>
+  </si>
+  <si>
+    <t>5826-21</t>
+  </si>
+  <si>
+    <t>5826-22</t>
+  </si>
+  <si>
+    <t>5826-23</t>
+  </si>
+  <si>
+    <t>5826-24</t>
+  </si>
+  <si>
+    <t>5826-25</t>
+  </si>
+  <si>
+    <t>5826-26</t>
+  </si>
+  <si>
+    <t>5826-27</t>
+  </si>
+  <si>
+    <t>5826-28</t>
+  </si>
+  <si>
+    <t>5826-29</t>
+  </si>
+  <si>
+    <t>5826-30</t>
+  </si>
+  <si>
+    <t>5826-31</t>
+  </si>
+  <si>
+    <t>5826-32</t>
+  </si>
+  <si>
+    <t>5826-33</t>
+  </si>
+  <si>
+    <t>5826-34</t>
+  </si>
+  <si>
+    <t>5826-35</t>
+  </si>
+  <si>
+    <t>5826-36</t>
+  </si>
+  <si>
+    <t>5826-37</t>
+  </si>
+  <si>
+    <t>5826-38</t>
+  </si>
+  <si>
+    <t>5826-39</t>
+  </si>
+  <si>
+    <t>5826-40</t>
+  </si>
+  <si>
+    <t>5826-41</t>
+  </si>
+  <si>
+    <t>5826-42</t>
+  </si>
+  <si>
+    <t>5826-43</t>
+  </si>
+  <si>
+    <t>5826-44</t>
+  </si>
+  <si>
+    <t>5826-45</t>
+  </si>
+  <si>
+    <t>5826-46</t>
+  </si>
+  <si>
+    <t>5826-47</t>
+  </si>
+  <si>
+    <t>5826-48</t>
+  </si>
+  <si>
+    <t>5826-49</t>
+  </si>
+  <si>
+    <t>5826-50</t>
+  </si>
+  <si>
+    <t>None taxable item</t>
+  </si>
+  <si>
+    <t>Non inv 1</t>
   </si>
 </sst>
 </file>
@@ -240,7 +360,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -261,6 +381,17 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -299,10 +430,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -311,6 +438,8 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,2128 +786,1998 @@
         <v>3</v>
       </c>
       <c r="G1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>10</v>
-      </c>
       <c r="I1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>42</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>10</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P2" s="7"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K3">
         <v>10</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K4">
         <v>10</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N4" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>45</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" t="s">
         <v>31</v>
       </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
       <c r="K5">
         <v>10</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>46</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K6">
         <v>10</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O6" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>47</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K7">
         <v>10</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>48</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K8">
         <v>10</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P8" s="7"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K9">
         <v>10</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O9" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" t="s">
         <v>31</v>
       </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
       <c r="K10">
         <v>10</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O10" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>51</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K11">
         <v>10</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O11" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>52</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K12">
         <v>10</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O12" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P12" s="7"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K13">
         <v>10</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K14">
         <v>10</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O14" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I15" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" t="s">
         <v>31</v>
       </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
       <c r="K15">
         <v>10</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K16">
         <v>10</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O16" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P16" s="7"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K17">
         <v>10</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O17" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P17" s="7"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K18">
         <v>10</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O18" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>59</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K19">
         <v>10</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O19" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>60</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" t="s">
         <v>31</v>
       </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
       <c r="K20">
         <v>10</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O20" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K21">
         <v>10</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>62</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K22">
         <v>10</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>63</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K23">
         <v>10</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>64</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K24">
         <v>10</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O24" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>65</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I25" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" t="s">
         <v>31</v>
       </c>
-      <c r="J25" t="s">
-        <v>32</v>
-      </c>
       <c r="K25">
         <v>10</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>66</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K26">
         <v>10</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>67</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K27">
         <v>10</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O27" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>68</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K28">
         <v>10</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K29">
         <v>10</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I30" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J30" t="s">
         <v>31</v>
       </c>
-      <c r="J30" t="s">
-        <v>32</v>
-      </c>
       <c r="K30">
         <v>10</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O30" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E31" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>71</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K31">
         <v>10</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O31" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="19">
-        <v>10</v>
-      </c>
-      <c r="L32" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M32" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N32" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O32" s="20" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="15"/>
+      <c r="G32" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="17">
+        <v>10</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O32" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="19">
-        <v>10</v>
-      </c>
-      <c r="L33" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M33" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N33" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O33" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="15"/>
+      <c r="G33" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="16" t="s">
         <v>30</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="17">
+        <v>10</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N33" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O33" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K34" s="19">
-        <v>10</v>
-      </c>
-      <c r="L34" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N34" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O34" s="20" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="17">
+        <v>10</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N34" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O34" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I35" s="18" t="s">
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="15"/>
+      <c r="G35" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J35" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K35" s="19">
-        <v>10</v>
-      </c>
-      <c r="L35" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M35" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N35" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O35" s="20" t="s">
-        <v>30</v>
+      <c r="K35" s="17">
+        <v>10</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N35" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O35" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H36" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="19">
-        <v>10</v>
-      </c>
-      <c r="L36" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M36" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N36" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" s="20" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F36" s="15"/>
+      <c r="G36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="17">
+        <v>10</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N36" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O36" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="19">
-        <v>10</v>
-      </c>
-      <c r="L37" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M37" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N37" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O37" s="20" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="15"/>
+      <c r="G37" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="17">
+        <v>10</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N37" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O37" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H38" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="19">
-        <v>10</v>
-      </c>
-      <c r="L38" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N38" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O38" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="15"/>
+      <c r="G38" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="16" t="s">
         <v>30</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="17">
+        <v>10</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H39" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="15"/>
+      <c r="G39" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="K39" s="19">
-        <v>10</v>
-      </c>
-      <c r="L39" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N39" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O39" s="20" t="s">
-        <v>30</v>
+      <c r="H39" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="17">
+        <v>10</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H40" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" s="15"/>
+      <c r="G40" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J40" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K40" s="19">
-        <v>10</v>
-      </c>
-      <c r="L40" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N40" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O40" s="20" t="s">
-        <v>30</v>
+      <c r="K40" s="17">
+        <v>10</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N40" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O40" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H41" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="19">
-        <v>10</v>
-      </c>
-      <c r="L41" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M41" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N41" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O41" s="20" t="s">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="15"/>
+      <c r="G41" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="17">
+        <v>10</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N41" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O41" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="19">
-        <v>10</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N42" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O42" s="20" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F42" s="15"/>
+      <c r="G42" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="17">
+        <v>10</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N42" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O42" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H43" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="19">
-        <v>10</v>
-      </c>
-      <c r="L43" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="15"/>
+      <c r="G43" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="16" t="s">
         <v>30</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="17">
+        <v>10</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N43" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O43" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K44" s="19">
-        <v>10</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N44" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O44" s="20" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="F44" s="15"/>
+      <c r="G44" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="17">
+        <v>10</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N44" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O44" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I45" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="15"/>
+      <c r="G45" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J45" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J45" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K45" s="19">
-        <v>10</v>
-      </c>
-      <c r="L45" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N45" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O45" s="20" t="s">
-        <v>30</v>
+      <c r="K45" s="17">
+        <v>10</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O45" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="F46" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="19">
-        <v>10</v>
-      </c>
-      <c r="L46" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M46" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O46" s="20" t="s">
-        <v>30</v>
+      <c r="D46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F46" s="15"/>
+      <c r="G46" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="17">
+        <v>10</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O46" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E47" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I47" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J47" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="19">
-        <v>10</v>
-      </c>
-      <c r="L47" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N47" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O47" s="20" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F47" s="15"/>
+      <c r="G47" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="17">
+        <v>10</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N47" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O47" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H48" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="19">
-        <v>10</v>
-      </c>
-      <c r="L48" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N48" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O48" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48" s="15"/>
+      <c r="G48" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" s="16" t="s">
         <v>30</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="17">
+        <v>10</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N48" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O48" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H49" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J49" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F49" s="15"/>
+      <c r="G49" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="K49" s="19">
-        <v>10</v>
-      </c>
-      <c r="L49" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N49" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O49" s="20" t="s">
-        <v>30</v>
+      <c r="H49" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="17">
+        <v>10</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N49" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O49" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E50" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I50" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50" s="15"/>
+      <c r="G50" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="J50" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="J50" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K50" s="19">
-        <v>10</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N50" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O50" s="20" t="s">
-        <v>30</v>
+      <c r="K50" s="17">
+        <v>10</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N50" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O50" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="G51" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H51" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="I51" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="19">
-        <v>10</v>
-      </c>
-      <c r="L51" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="N51" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="O51" s="20" t="s">
-        <v>30</v>
+        <v>40</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51" s="15"/>
+      <c r="G51" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="17">
+        <v>10</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N51" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="O51" s="18" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2789,7 +2788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" style="1" customWidth="1"/>
@@ -2810,24 +2809,24 @@
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>50</v>
       </c>
       <c r="C2" s="14">
         <v>5</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="14">
         <v>10</v>
@@ -2835,16 +2834,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C3" s="14">
         <v>5</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="14">
         <v>10</v>
@@ -2852,16 +2851,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C4" s="14">
         <v>5</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="14">
         <v>10</v>
@@ -2869,44 +2868,42 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="14"/>
+        <v>93</v>
+      </c>
+      <c r="C5" s="14">
+        <v>5</v>
+      </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C6" s="14">
         <v>5</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="14">
-        <v>10</v>
-      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C7" s="14">
         <v>5</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E7" s="14">
         <v>10</v>
@@ -2914,16 +2911,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C8" s="14">
         <v>5</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="14">
         <v>10</v>
@@ -2931,200 +2928,275 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+        <v>33</v>
+      </c>
+      <c r="C9" s="14">
+        <v>5</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>47</v>
+      <c r="A10" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="C10" s="14">
         <v>5</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="14">
-        <v>10</v>
-      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>47</v>
+      <c r="A11" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C11" s="14">
         <v>5</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="14">
-        <v>10</v>
-      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>47</v>
+      <c r="A12" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C12" s="14">
         <v>5</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E12" s="14">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>47</v>
+      <c r="A13" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+        <v>92</v>
+      </c>
+      <c r="C13" s="14">
+        <v>5</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>48</v>
+      <c r="A14" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C14" s="14">
         <v>5</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E14" s="14">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
+      <c r="A15" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="C15" s="14">
         <v>5</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="14">
-        <v>10</v>
-      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>48</v>
+      <c r="A16" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C16" s="14">
         <v>5</v>
       </c>
-      <c r="D16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="14">
-        <v>10</v>
-      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>48</v>
+      <c r="A17" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="14">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
+      <c r="A18" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="C18" s="14">
         <v>5</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E18" s="14">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
+      <c r="A19" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C19" s="14">
         <v>5</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" s="14">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>49</v>
+      <c r="A20" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C20" s="14">
         <v>5</v>
       </c>
-      <c r="D20" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="14">
-        <v>10</v>
-      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>49</v>
+      <c r="A21" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="14"/>
+        <v>36</v>
+      </c>
+      <c r="C21" s="14">
+        <v>5</v>
+      </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="14">
+        <v>5</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="14">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="14">
+        <v>5</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="19">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
